--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -24,9 +24,9 @@
       <text>
         <r>
           <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。</t>
+已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
         </r>
       </text>
     </comment>
@@ -34,9 +34,9 @@
       <text>
         <r>
           <t xml:space="preserve">运动员
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。</t>
+无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
         </r>
       </text>
     </comment>
@@ -44,9 +44,9 @@
       <text>
         <r>
           <t xml:space="preserve">队伍
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：一队
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。</t>
+使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队</t>
         </r>
       </text>
     </comment>
@@ -56,7 +56,7 @@
           <t xml:space="preserve">训练日期
 必填｜YYYY-MM-DD
 例：2026-10-01
-必须填写本次记录的真实日期；不自动补今天。</t>
+必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01</t>
         </r>
       </text>
     </comment>
@@ -64,9 +64,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练场次
-条件必填｜无单位
+条件必填：同一人同一天有多次训练时填写
 例：上午力量
-同人同日多课必须明确所属课次；仅一课可使用默认值。</t>
+同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量</t>
         </r>
       </text>
     </comment>
@@ -74,9 +74,9 @@
       <text>
         <r>
           <t xml:space="preserve">动作
-必填｜无单位
+必填
 例：深蹲
-填写实际记录。</t>
+填写实际记录。 例：深蹲</t>
         </r>
       </text>
     </comment>
@@ -84,9 +84,9 @@
       <text>
         <r>
           <t xml:space="preserve">组次
-条件必填｜无单位
+条件必填：同一动作做了多组时填写
 例：1
-同动作多组必须区分组序；仅一组可默认1。</t>
+同动作多组必须区分组序；仅一组可默认1。 例：1</t>
         </r>
       </text>
     </comment>
@@ -96,7 +96,7 @@
           <t xml:space="preserve">实际次数
 必填｜次
 例：6
-填写实际记录。</t>
+填写实际记录。 例：6</t>
         </r>
       </text>
     </comment>
@@ -106,7 +106,7 @@
           <t xml:space="preserve">实际重量kg
 必填｜kg
 例：60
-真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。</t>
+真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60</t>
         </r>
       </text>
     </comment>
@@ -114,9 +114,10 @@
       <text>
         <r>
           <t xml:space="preserve">RPE
-选填｜无单位
+主观用力程度：运动员觉得这次训练有多累
+选填
 例：6
-0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。</t>
+主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
         </r>
       </text>
     </comment>
@@ -124,10 +125,9 @@
       <text>
         <r>
           <t xml:space="preserve">是否完成
-选填｜无单位
+选填
 例：是
-仅填写实际已采集数据，未提供留空。
-可选值：是、否</t>
+仅填写实际已采集数据，未提供留空。 例：是 可选：是、否</t>
         </r>
       </text>
     </comment>
@@ -135,9 +135,9 @@
       <text>
         <r>
           <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：本次实测</t>
         </r>
       </text>
     </comment>
@@ -145,9 +145,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练项目（小项）
-选填｜无单位
+选填
 例：男子双人划艇
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：男子双人划艇</t>
         </r>
       </text>
     </comment>
@@ -155,10 +155,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练类型
-选填｜无单位
+选填
 例：基础力量
-仅填写实际已采集数据，未提供留空。
-可选值：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
+仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
         </r>
       </text>
     </comment>
@@ -166,10 +165,9 @@
       <text>
         <r>
           <t xml:space="preserve">身体位置
-选填｜无单位
+选填
 例：下肢
-仅填写实际已采集数据，未提供留空。
-可选值：上肢、下肢、核心、全身</t>
+仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身</t>
         </r>
       </text>
     </comment>
@@ -177,10 +175,9 @@
       <text>
         <r>
           <t xml:space="preserve">训练环境
-选填｜无单位
+选填
 例：陆上
-仅填写实际已采集数据，未提供留空。
-可选值：水上、陆上、测功仪、泳池、场馆、其他</t>
+仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他</t>
         </r>
       </text>
     </comment>
@@ -190,7 +187,7 @@
           <t xml:space="preserve">计划次数
 选填｜次
 例：6
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：6</t>
         </r>
       </text>
     </comment>
@@ -200,7 +197,7 @@
           <t xml:space="preserve">计划重量kg
 选填｜kg
 例：60
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：60</t>
         </r>
       </text>
     </comment>
@@ -208,9 +205,10 @@
       <text>
         <r>
           <t xml:space="preserve">强度%
+按原训练记录给出的强度百分比
 选填｜%
 例：80
-仅填写实际已采集数据，未提供留空。</t>
+按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。</t>
         </r>
       </text>
     </comment>
@@ -218,10 +216,10 @@
       <text>
         <r>
           <t xml:space="preserve">强度区间
-选填｜无单位
+原训练记录采用的强度分区
+选填
 例：U2
-仅填写实际已采集数据，未提供留空。
-可选值：U3、U2、U1、AT、TPT、AN、ATP</t>
+原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
         </r>
       </text>
     </comment>
@@ -231,7 +229,7 @@
           <t xml:space="preserve">训练时间min
 选填｜min
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -241,7 +239,7 @@
           <t xml:space="preserve">训练距离km
 选填｜km
 例：12.5
-仅填写实际已采集数据，未提供留空。</t>
+仅填写实际已采集数据，未提供留空。 例：12.5</t>
         </r>
       </text>
     </comment>
@@ -250,7 +248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>竞迹｜体能训练结果导入模板</t>
   </si>
@@ -282,10 +280,13 @@
     <t>8. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>9. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
-  </si>
-  <si>
-    <t>10. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>9. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+  </si>
+  <si>
+    <t>10. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>11. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>训练结果数据</t>
@@ -295,17 +296,17 @@
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
-系统预填｜无单位
+系统预填
 例：系统生成</t>
   </si>
   <si>
     <t xml:space="preserve">运动员
-条件必填｜无单位
+条件必填：没有系统编号，或新建人员时填写
 例：张某</t>
   </si>
   <si>
     <t xml:space="preserve">队伍
-条件必填｜无单位
+条件必填：未由当前项目、队伍预填时填写
 例：一队</t>
   </si>
   <si>
@@ -315,17 +316,17 @@
   </si>
   <si>
     <t xml:space="preserve">训练场次
-条件必填｜无单位
+条件必填：同一人同一天有多次训练时填写
 例：上午力量</t>
   </si>
   <si>
     <t xml:space="preserve">动作
-必填｜无单位
+必填
 例：深蹲</t>
   </si>
   <si>
     <t xml:space="preserve">组次
-条件必填｜无单位
+条件必填：同一动作做了多组时填写
 例：1</t>
   </si>
   <si>
@@ -340,37 +341,38 @@
   </si>
   <si>
     <t xml:space="preserve">RPE
-选填｜无单位
+主观用力程度：运动员觉得这次训练有多累
+选填
 例：6</t>
   </si>
   <si>
     <t xml:space="preserve">是否完成
-选填｜无单位
+选填
 例：是</t>
   </si>
   <si>
     <t xml:space="preserve">备注
-选填｜无单位
+选填
 例：本次实测</t>
   </si>
   <si>
     <t xml:space="preserve">训练项目（小项）
-选填｜无单位
+选填
 例：男子双人划艇</t>
   </si>
   <si>
     <t xml:space="preserve">训练类型
-选填｜无单位
+选填
 例：基础力量</t>
   </si>
   <si>
     <t xml:space="preserve">身体位置
-选填｜无单位
+选填
 例：下肢</t>
   </si>
   <si>
     <t xml:space="preserve">训练环境
-选填｜无单位
+选填
 例：陆上</t>
   </si>
   <si>
@@ -385,12 +387,14 @@
   </si>
   <si>
     <t xml:space="preserve">强度%
+按原训练记录给出的强度百分比
 选填｜%
 例：80</t>
   </si>
   <si>
     <t xml:space="preserve">强度区间
-选填｜无单位
+原训练记录采用的强度分区
+选填
 例：U2</t>
   </si>
   <si>
@@ -839,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -902,6 +906,11 @@
     <row r="12" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +937,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -954,7 +963,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -978,72 +987,72 @@
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
     </row>
-    <row r="3" ht="82" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -3053,136 +3062,136 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统预填｜无单位" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜YYYY-MM-DD" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜YYYY-MM-DD" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜无单位" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="条件必填｜无单位" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜次" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜次" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜kg" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="必填｜kg" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="0—10；未采集留空。时长与RPE齐全时系统计算SRPE；缺RPE仍可导入。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：是" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：是" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：下肢" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：下肢" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：陆上" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：陆上" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜次" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜次" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜kg" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="仅填写实际已采集数据，未提供留空。 例：80" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜%" prompt="仅填写实际已采集数据，未提供留空。 例：80" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="选填｜无单位" prompt="仅填写实际已采集数据，未提供留空。 例：U2" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜min" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜km" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="选填｜km" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -256,10 +256,10 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 常用列在前；专业选填列在右侧默认收起，点左上角分组级别“2”展开。不支持分组时使用取消隐藏列；不使用宏。</t>
-  </si>
-  <si>
-    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。隐藏列有值仍会校验和导入。</t>
+    <t>1. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+  </si>
+  <si>
+    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
   </si>
   <si>
     <t>3. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
@@ -292,7 +292,7 @@
     <t>训练结果数据</t>
   </si>
   <si>
-    <t>每位运动员每个动作每组一行；动作、实际次数和实际重量必填，同动作多组需组次，同日多课需训练场次。徒手实际外加重量填0；时长按原记录填写，不在每组重复填整课时长。 专业选填列已收起，点左上角分组级别“2”展开；不支持分组时取消隐藏列。详情见列批注。</t>
+    <t>每位运动员每个动作每组一行；动作、实际次数和实际重量必填，同动作多组需组次，同日多课需训练场次。徒手实际外加重量填0；时长按原记录填写，不在每组重复填整课时长。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
@@ -921,18 +921,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:V503"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="1" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="3" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22" style="4" customWidth="1"/>
     <col min="5" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="22" width="22" hidden="1" outlineLevel="1" collapsed="1" customWidth="1"/>
+    <col min="13" max="22" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -248,7 +248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>竞迹｜体能训练结果导入模板</t>
   </si>
@@ -256,37 +256,40 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
-  </si>
-  <si>
-    <t>2. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
-  </si>
-  <si>
-    <t>3. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
-  </si>
-  <si>
-    <t>4. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
-  </si>
-  <si>
-    <t>5. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
-  </si>
-  <si>
-    <t>6. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
-  </si>
-  <si>
-    <t>7. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
-  </si>
-  <si>
-    <t>8. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
-  </si>
-  <si>
-    <t>9. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
-  </si>
-  <si>
-    <t>10. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
-  </si>
-  <si>
-    <t>11. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>1. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
+  </si>
+  <si>
+    <t>2. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+  </si>
+  <si>
+    <t>3. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+  </si>
+  <si>
+    <t>4. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+  </si>
+  <si>
+    <t>5. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+  </si>
+  <si>
+    <t>6. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+  </si>
+  <si>
+    <t>7. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+  </si>
+  <si>
+    <t>8. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+  </si>
+  <si>
+    <t>9. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+  </si>
+  <si>
+    <t>10. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+  </si>
+  <si>
+    <t>11. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>12. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>训练结果数据</t>
@@ -415,7 +418,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -434,10 +437,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF334155"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF422006"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,17 +462,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF52747C"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF345D68"/>
+        <fgColor rgb="FFF59E0B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF193A44"/>
+        <fgColor rgb="FF991B1B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D4ED8"/>
       </patternFill>
     </fill>
   </fills>
@@ -492,16 +508,16 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -843,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -911,6 +927,11 @@
     <row r="13" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +955,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -960,7 +981,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -986,70 +1007,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -248,7 +248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>竞迹｜体能训练结果导入模板</t>
   </si>
@@ -256,40 +256,43 @@
     <t>jingji-import-v2</t>
   </si>
   <si>
-    <t>1. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
-  </si>
-  <si>
-    <t>2. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
-  </si>
-  <si>
-    <t>3. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
-  </si>
-  <si>
-    <t>4. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
-  </si>
-  <si>
-    <t>5. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
-  </si>
-  <si>
-    <t>6. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
-  </si>
-  <si>
-    <t>7. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
-  </si>
-  <si>
-    <t>8. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
-  </si>
-  <si>
-    <t>9. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
-  </si>
-  <si>
-    <t>10. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
-  </si>
-  <si>
-    <t>11. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
-  </si>
-  <si>
-    <t>12. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>1. 其他测试：选择中文测试项目（如纵跳（cm）），再填成绩（如45）；系统自动匹配指标和单位，无需填写代码。找不到项目时请管理员先配置，不要编造名称。</t>
+  </si>
+  <si>
+    <t>2. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
+  </si>
+  <si>
+    <t>3. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+  </si>
+  <si>
+    <t>4. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+  </si>
+  <si>
+    <t>5. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+  </si>
+  <si>
+    <t>6. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+  </si>
+  <si>
+    <t>7. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+  </si>
+  <si>
+    <t>8. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+  </si>
+  <si>
+    <t>9. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+  </si>
+  <si>
+    <t>10. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+  </si>
+  <si>
+    <t>11. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+  </si>
+  <si>
+    <t>12. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>13. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>训练结果数据</t>
@@ -859,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -932,6 +935,11 @@
     <row r="14" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +963,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -981,7 +989,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1007,70 +1015,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">

--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -248,7 +248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>竞迹｜体能训练结果导入模板</t>
   </si>
@@ -262,37 +262,40 @@
     <t>2. 表头颜色：红色=必填，橙色=满足说明中的条件才必填，蓝色=选填，灰色=系统预填；具体填写要求以表头文字为准。</t>
   </si>
   <si>
-    <t>3. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
-  </si>
-  <si>
-    <t>4. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
-  </si>
-  <si>
-    <t>5. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
-  </si>
-  <si>
-    <t>6. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
-  </si>
-  <si>
-    <t>7. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
-  </si>
-  <si>
-    <t>8. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
-  </si>
-  <si>
-    <t>9. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
-  </si>
-  <si>
-    <t>10. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
-  </si>
-  <si>
-    <t>11. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
-  </si>
-  <si>
-    <t>12. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
-  </si>
-  <si>
-    <t>13. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
+    <t>3. 有固定选项的字段直接点击单元格下拉选择；无需手写内部代码。空白表示未提供，不用选择任意值占位。</t>
+  </si>
+  <si>
+    <t>4. 必填项在前，选填项在后；常用选填项排在专业选填项前面，所有数据列直接显示，按需填写即可。</t>
+  </si>
+  <si>
+    <t>5. 第1—3行是说明和表头，第4行起填写；示例仅在表头，不需要删除示例数据。所有已填写的数据都会校验和导入。</t>
+  </si>
+  <si>
+    <t>6. 业务日期须在行内填写，或在上传页明确选择统一日期；新模板不静默使用今天，生日永不补填。</t>
+  </si>
+  <si>
+    <t>7. 系统预填：授权范围内的人员编号、姓名、项目和队伍；不要自行编造编号，不预填测量成绩。</t>
+  </si>
+  <si>
+    <t>8. SRPE：有效时长(min)×RPE，单位AU；缺时长或RPE保持未提供，不能根据距离推算时长。</t>
+  </si>
+  <si>
+    <t>9. SMVL/力量训练量：按现有规则汇总实际次数×实际重量kg；计划数不是实际数，外部显式总量沿用既有优先策略。</t>
+  </si>
+  <si>
+    <t>10. FMS：七项齐全才生成完整21分制总分，未测不补0。专项：按有效轮次计算平均、最好及同条件排名；无可比历史显示缺失。</t>
+  </si>
+  <si>
+    <t>11. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
+  </si>
+  <si>
+    <t>12. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+  </si>
+  <si>
+    <t>13. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+  </si>
+  <si>
+    <t>14. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
   </si>
   <si>
     <t>训练结果数据</t>
@@ -862,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -940,6 +943,11 @@
     <row r="15" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +971,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -989,7 +997,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1015,70 +1023,70 @@
     </row>
     <row r="3" ht="89" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -3088,136 +3096,136 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
       <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
       <formula1>"上肢,下肢,核心,全身"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
       <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
       <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
+      <formula1>TRUE</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/templates/竞迹体能训练数据导入模板.xlsx
+++ b/public/templates/竞迹体能训练数据导入模板.xlsx
@@ -14,239 +14,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">系统运动员编号
-系统预填
-例：系统生成
-已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">运动员
-条件必填：没有系统编号，或新建人员时填写
-例：张某
-无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">队伍
-条件必填：未由当前项目、队伍预填时填写
-例：一队
-使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练日期
-必填｜YYYY-MM-DD
-例：2026-10-01
-必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练场次
-条件必填：同一人同一天有多次训练时填写
-例：上午力量
-同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">动作
-必填
-例：深蹲
-填写实际记录。 例：深蹲</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">组次
-条件必填：同一动作做了多组时填写
-例：1
-同动作多组必须区分组序；仅一组可默认1。 例：1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">实际次数
-必填｜次
-例：6
-填写实际记录。 例：6</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">实际重量kg
-必填｜kg
-例：60
-真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">RPE
-主观用力程度：运动员觉得这次训练有多累
-选填
-例：6
-主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">是否完成
-选填
-例：是
-仅填写实际已采集数据，未提供留空。 例：是 可选：是、否</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">备注
-选填
-例：本次实测
-仅填写实际已采集数据，未提供留空。 例：本次实测</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练项目（小项）
-选填
-例：男子双人划艇
-仅填写实际已采集数据，未提供留空。 例：男子双人划艇</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练类型
-选填
-例：基础力量
-仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">身体位置
-选填
-例：下肢
-仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练环境
-选填
-例：陆上
-仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">计划次数
-选填｜次
-例：6
-仅填写实际已采集数据，未提供留空。 例：6</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">计划重量kg
-选填｜kg
-例：60
-仅填写实际已采集数据，未提供留空。 例：60</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">强度%
-按原训练记录给出的强度百分比
-选填｜%
-例：80
-按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">强度区间
-原训练记录采用的强度分区
-选填
-例：U2
-原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练时间min
-选填｜min
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V3" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">训练距离km
-选填｜km
-例：12.5
-仅填写实际已采集数据，未提供留空。 例：12.5</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
@@ -289,10 +56,10 @@
     <t>11. 年龄由真实生日计算；冠军模型、雷达图和参考值由系统分析，不要求填报。Excel公式不作为计算事实源。</t>
   </si>
   <si>
-    <t>12. 表头写明何时填写；点击填写单元格可看解释、填写例子和不知道时的处理办法，详细说明也在表头批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
-  </si>
-  <si>
-    <t>13. 必填条件见列批注。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
+    <t>12. 表头写明何时填写、通俗解释和填写示例，不设置单元格弹出提示或批注。示例评分表名仅演示格式，请用真实依据，不代表系统提供该标准。</t>
+  </si>
+  <si>
+    <t>13. 必填条件见表头。空白是未提供，真实0保留；非法文本报错。仅预填身份和日期的业务行自动忽略。</t>
   </si>
   <si>
     <t>14. 已有记录只按非空值更新，空白保留已有值；跨项目、越权、同名歧义及同日多课归属必须在提交前解决。</t>
@@ -301,7 +68,7 @@
     <t>训练结果数据</t>
   </si>
   <si>
-    <t>每位运动员每个动作每组一行；动作、实际次数和实际重量必填，同动作多组需组次，同日多课需训练场次。徒手实际外加重量填0；时长按原记录填写，不在每组重复填整课时长。 必填项在前，选填项在后；所有数据列直接显示，按需填写。详情见列批注。</t>
+    <t>每位运动员每个动作每组一行；动作、实际次数和实际重量必填，同动作多组需组次，同日多课需训练场次。徒手实际外加重量填0；时长按原记录填写，不在每组重复填整课时长。 必填项在前，选填项在后；所有数据列直接显示，按需填写。填写要求见表头。</t>
   </si>
   <si>
     <t xml:space="preserve">系统运动员编号
@@ -3095,142 +2862,63 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="44">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:A503">
+  <dataValidations count="18">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A10:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="系统运动员编号：怎么填" prompt="已有人员编号优先定位，不可自行编造；无编号时按姓名、项目和队伍确认。 例：系统生成" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:A503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="A4:J503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B10:B503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:M503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="运动员：怎么填" prompt="无有效系统编号或新建人员时必填；已有人员预填供核对。 例：张某" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="B4:B503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:M503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C10:C503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
+      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
+      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
+      <formula1>"上肢,下肢,核心,全身"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
+      <formula1>"上肢,下肢,核心,全身"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
+      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
+      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:S503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="队伍：怎么填" prompt="使用已明确的授权项目、队伍；可由上下文预填，不得跨项目或通过导入调队。 例：一队" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="C4:C503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:S503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D10:D503">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
+      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
+      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练日期：怎么填" prompt="必须填写本次记录的真实日期；不自动补今天。 例：2026-10-01" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="D4:D503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E10:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练场次：怎么填" prompt="同人同日多课必须明确所属课次；仅一课可使用默认值。 例：上午力量" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="E4:E503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F10:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="动作：怎么填" prompt="填写实际记录。 例：深蹲" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="F4:F503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G10:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="组次：怎么填" prompt="同动作多组必须区分组序；仅一组可默认1。 例：1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="G4:G503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H10:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际次数：怎么填" prompt="填写实际记录。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="H4:H503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I10:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="实际重量kg：怎么填" prompt="真实外加重量；徒手可填0，未采集留空并纠错，不能编造0。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="I4:I503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J10:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="RPE：怎么填" prompt="主观用力程度：运动员觉得这次训练有多累。怎么填：填写运动员本人按队内现行0—10量表报告的分数，不按心率或教练印象代算。例：6。为什么：结合训练时长计算本次主观训练负荷，单独看时长不能说明本人感受。不知道时：没有询问或采集就留空，不填0代替；仍可导入训练时长、距离。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="J4:J503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K10:K503">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="是否完成：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：是 可选：是、否" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：是、否" sqref="K4:K503">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L10:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="备注：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：本次实测" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="L4:L503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M10:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练项目（小项）：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：男子双人划艇" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="M4:M503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N10:N503">
-      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练类型：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：基础力量 可选：基础力量、功能性体能、核心力量、专项力量、代谢训练" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：基础力量、功能性体能、核心力量、专项力量、代谢训练" sqref="N4:N503">
-      <formula1>"基础力量,功能性体能,核心力量,专项力量,代谢训练"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O10:O503">
-      <formula1>"上肢,下肢,核心,全身"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="身体位置：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：下肢 可选：上肢、下肢、核心、全身" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：上肢、下肢、核心、全身" sqref="O4:O503">
-      <formula1>"上肢,下肢,核心,全身"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P10:P503">
-      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="训练环境：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：陆上 可选：水上、陆上、测功仪、泳池、场馆、其他" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：水上、陆上、测功仪、泳池、场馆、其他" sqref="P4:P503">
-      <formula1>"水上,陆上,测功仪,泳池,场馆,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q10:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划次数：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：6" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="Q4:Q503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R10:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="计划重量kg：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：60" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="R4:R503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S10:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="强度%：怎么填" prompt="按原训练记录给出的强度百分比。怎么填：已有记录为80%时填80；它不是RPE，也不是让你自行选一个百分比。例：80。为什么：保留原训练记录使用的强度信息。不知道时：原记录没有就留空，不根据重量自行估算。" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="S4:S503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T10:T503">
-      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="强度区间：怎么填" prompt="原训练记录采用的强度分区。怎么填：只有队内训练记录明确标了U2、AT等分区时才选择相同项。例：U2。为什么：用于按原有分区整理训练内容，不代表系统已替你测定强度。不知道时：没有明确分区就留空，不根据这份模板自行判断。" showErrorMessage="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：U3、U2、U1、AT、TPT、AN、ATP" sqref="T4:T503">
-      <formula1>"U3,U2,U1,AT,TPT,AN,ATP"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U10:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练时间min：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:U503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V10:V503">
-      <formula1>TRUE</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" promptTitle="训练距离km：怎么填" prompt="仅填写实际已采集数据，未提供留空。 例：12.5" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="V4:V503">
+    <dataValidation type="custom" allowBlank="1" errorStyle="stop" errorTitle="请检查填写值" error="请选择：按列说明填写" sqref="U4:V503">
       <formula1>TRUE</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>